--- a/expenditure-analysis.xlsx
+++ b/expenditure-analysis.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="139">
   <si>
     <t xml:space="preserve">Category</t>
   </si>
@@ -67,7 +67,7 @@
     <t xml:space="preserve">Net Profit</t>
   </si>
   <si>
-    <t xml:space="preserve">p.s. ATM no deductions</t>
+    <t xml:space="preserve">p.s. ATM no deductions, only flat rate</t>
   </si>
   <si>
     <t xml:space="preserve">Gross Profit Margin</t>
@@ -440,6 +440,9 @@
   </si>
   <si>
     <t xml:space="preserve">Losses on Disposal of Non-Operating Assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TODO</t>
   </si>
 </sst>
 </file>
@@ -1114,7 +1117,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36.8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2717,7 +2720,13 @@
   </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>138</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
